--- a/nurse_forms/005_next_of_kin_form--nurse_forms.xlsx
+++ b/nurse_forms/005_next_of_kin_form--nurse_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +432,7 @@
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -699,7 +699,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Relationship</t>
+          <t>Emergency Contact Relationship</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -745,7 +745,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Emergency Contact Phone</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,7 +768,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Emergency Contact Email</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,7 +791,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>Emergency Contact Address</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -837,7 +837,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Relationship</t>
+          <t>Other Next Of Kin Relationship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,7 +860,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Next Of Kin Name</t>
+          <t>Other Next Of Kin Name</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,7 +883,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Other Next Of Kin Phone</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,7 +906,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Other Next Of Kin Email</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,7 +929,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>Other Next Of Kin Address</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -998,7 +998,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Date Of Birth</t>
+          <t>Emergency Contact Dob</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
